--- a/instance/tournament_3_schedule.xlsx
+++ b/instance/tournament_3_schedule.xlsx
@@ -453,13 +453,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -534,12 +534,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 1</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 2</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -583,27 +583,27 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>BYE</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -632,27 +632,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -691,17 +691,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Edward Wang / Dominic Pang</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Hancheng Li / Zhuoran Cheng</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -745,12 +745,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang / Dominic Pang</t>
+          <t>Charles Yang / Haipeng Huang</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Charles Yang / Haipeng Huang</t>
+          <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -784,22 +784,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Janice Lee / Cindy Lim</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Hanna Yun / Cynthia Liu</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -828,12 +828,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Rishi Jain</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee / Cindy Lim</t>
+          <t>Midy Tao</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -877,27 +877,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Reyna Wan / Elisa Liu</t>
+          <t>Vincent Onggoputra</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Stephen Guan</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -936,17 +936,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 3</t>
+          <t>Martin Lee</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 4</t>
+          <t>Shan Zhong</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -975,12 +975,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
+          <t>Ines Bocanegra</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>Fanghong Huang</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -1014,106 +1014,114 @@
       <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Court 5</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung / Jason Liu</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung, Jason Liu</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Shan Zhong</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Shiyang Chang</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Fanghong Huang</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Ryuto Leegomonchai</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -1127,27 +1135,27 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 1</t>
+          <t>Zain Merchant</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 2</t>
+          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 1, Winner of Match 2</t>
+          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1190,17 +1198,17 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 1</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 2</t>
+          <t>Haocheng Teng</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 1, Winner of Match 2</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1228,27 +1236,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang / Dominic Pang</t>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao / Stephen Guan</t>
+          <t>Dominic Pang</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1277,27 +1285,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Charles Yang / Haipeng Huang</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1331,7 +1339,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1341,12 +1349,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1365,249 +1373,269 @@
       <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu, Aryan Khandekar, Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal / Haonan Wang</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal, Prathamesh Koranne, Haonan Wang, Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Vincent Onggoputra</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>BYE</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung, Jason Liu</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>WD</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Sirui Jiang / Yen Zhen Tan</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Janice Lee / Cindy Lim</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Meghan Wong / Makenna Wong</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Meghan Wong, Makenna Wong</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Reyna Wan / Elisa Liu</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match 3</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match 4</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung / Jason Liu</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne, Yuhung Kung, Jason Liu, Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1620,32 +1648,32 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 1</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 2</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 1, Winner of Match 2</t>
+          <t>Avi Aswal, Haonan Wang</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1663,77 +1691,159 @@
       <c r="M24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal / Haonan Wang</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal, Aryan Khandekar, Haonan Wang, Heng Wu</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu, Aryan Khandekar, Yifei Zheng, Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Court 2</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Winner of Match 1, Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1746,27 +1856,27 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Winner of Winner of Match 3</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao / Stephen Guan</t>
+          <t>Winner of Winner of Match 4</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -1795,12 +1905,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1810,12 +1920,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -1844,12 +1954,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1859,12 +1969,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -1883,912 +1993,197 @@
       <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" t="n">
         <v>5</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Edward Wang</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Rishi Jain</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Martin Lee</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Dominic Pang</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="32"/>
     <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Hanna Yun / Cynthia Liu</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Sirui Jiang / Yen Zhen Tan</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Meghan Wong / Makenna Wong</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Total Affected Players</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match 3</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>BYE</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Consecutive 4 times</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Yijun Liu</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Janice Lee</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Jason Liu</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Consecutive 4 times</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Court 6</t>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Consecutive 4 times</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>6</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Court 1</t>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Heng Wu</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Edward Wang / Dominic Pang</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Avi Aswal</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Charles Yang / Haipeng Huang</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Midy Tao / Stephen Guan</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Haonan Wang</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Zain Merchant</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Meghan Wong</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Ryuto Leegomonchai</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Makenna Wong</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Ines Bocanegra</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>BYE</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Haocheng Teng</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>8</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>8</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>8</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>8</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>9</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>9</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>9</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>9</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>9</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Stats</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr"/>
-      <c r="C58" s="4" t="inlineStr"/>
-      <c r="D58" s="4" t="inlineStr"/>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
-      <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="4" t="inlineStr"/>
-      <c r="K58" s="4" t="inlineStr"/>
-      <c r="L58" s="4" t="inlineStr"/>
-      <c r="M58" s="4" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Total Affected Players</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr"/>
-      <c r="C59" s="5" t="inlineStr"/>
-      <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="5" t="inlineStr"/>
-      <c r="G59" s="5" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
-      <c r="K59" s="5" t="inlineStr"/>
-      <c r="L59" s="5" t="inlineStr"/>
-      <c r="M59" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
         </is>
       </c>
     </row>

--- a/instance/tournament_3_schedule.xlsx
+++ b/instance/tournament_3_schedule.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,7 +603,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -647,7 +647,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang / Dominic Pang</t>
+          <t>Midy Tao / Stephen Guan</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
+          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Charles Yang / Haipeng Huang</t>
+          <t>Janice Lee / Cindy Lim</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Sirui Jiang / Yen Zhen Tan</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -779,12 +779,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee / Cindy Lim</t>
+          <t>Brandon Pham</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Edward Wang</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -828,12 +828,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Rishi Jain</t>
+          <t>Charles Yang / Haipeng Huang</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao</t>
+          <t>Hancheng Li / Zhuoran Cheng</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -887,17 +887,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Vincent Onggoputra</t>
+          <t>Shan Zhong</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Dominic Pang</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -941,12 +941,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>Martin Lee</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Shan Zhong</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -980,22 +980,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Ines Bocanegra</t>
+          <t>Zain Merchant</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Fanghong Huang</t>
+          <t>Ryuto Leegomonchai</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -1014,216 +1014,200 @@
       <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Court 5</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Fanghong Huang</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Yijun Liu</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Shiyang Chang</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Ines Bocanegra</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Yuhung Kung, Jason Liu</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Ryuto Leegomonchai</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Zain Merchant</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Avi Aswal</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Haocheng Teng</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1246,17 +1230,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1285,12 +1269,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1300,12 +1284,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1334,27 +1318,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Midy Tao</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Reyna Wan / Elisa Liu</t>
+          <t>Stephen Guan</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1373,57 +1357,53 @@
       <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Heng Wu, Aryan Khandekar, Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Jason Liu</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1461,7 +1441,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal, Prathamesh Koranne, Haonan Wang, Manmeeth Nagesh</t>
+          <t>Manmeeth Nagesh, Avi Aswal, Haonan Wang</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1504,17 +1484,17 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung, Jason Liu</t>
+          <t>Yifei Zheng, Juncheng Tang</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1557,17 +1537,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Meghan Wong, Makenna Wong</t>
+          <t>Bernice Tse Ling Tung, Tsz Ching Chen</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1620,7 +1600,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne, Yuhung Kung, Jason Liu, Manmeeth Nagesh</t>
+          <t>Jason Liu, Manmeeth Nagesh, Yuhung Kung</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1673,7 +1653,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal, Haonan Wang</t>
+          <t>Yifei Zheng, Haonan Wang, Avi Aswal, Juncheng Tang</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1716,7 +1696,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1726,7 +1706,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal, Aryan Khandekar, Haonan Wang, Heng Wu</t>
+          <t>Yuhung Kung, Jason Liu</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1769,17 +1749,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
           <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu, Aryan Khandekar, Yifei Zheng, Juncheng Tang</t>
+          <t>Prathamesh Koranne, Manmeeth Nagesh, Yifei Zheng, Juncheng Tang</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1797,53 +1777,57 @@
       <c r="M26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Court 2</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal / Haonan Wang</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Haonan Wang, Aryan Khandekar, Avi Aswal, Heng Wu</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1871,12 +1855,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Winner of Winner of Match 3</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Winner of Winner of Match 4</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -1920,12 +1904,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Winner of Winner of Match 1</t>
+          <t>Winner of Winner of Match 3</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Winner of Winner of Match 2</t>
+          <t>Winner of Winner of Match 4</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -1964,7 +1948,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1993,132 +1977,198 @@
       <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-    </row>
-    <row r="32"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+    </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Court 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Stats</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr"/>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr"/>
-      <c r="L33" s="4" t="inlineStr"/>
-      <c r="M33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Total Affected Players</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="n">
+      <c r="B40" s="5" t="inlineStr"/>
+      <c r="C40" s="5" t="inlineStr"/>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="n">
         <v>12</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Heng Wu</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
       </c>
     </row>
     <row r="41">
       <c r="F41" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2130,58 +2180,130 @@
     <row r="42">
       <c r="F42" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Consecutive 2 times</t>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="F43" t="inlineStr">
         <is>
-          <t>Meghan Wong</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="F44" t="inlineStr">
         <is>
-          <t>Makenna Wong</t>
+          <t>Yifei Zheng</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="F45" t="inlineStr">
         <is>
-          <t>Yifei Zheng</t>
+          <t>Juncheng Tang</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="F46" t="inlineStr">
         <is>
-          <t>Juncheng Tang</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tsz Ching Chen</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Heng Wu</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>Consecutive 1 times</t>
         </is>
